--- a/VerveStacks_POL_grids_syn_5/SuppXLS/trades/scentrade__trade_links.xlsx
+++ b/VerveStacks_POL_grids_syn_5/SuppXLS/trades/scentrade__trade_links.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29231"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29328"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_POL_grids_syn_5\SuppXLS\trades\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{4980DEA9-3343-4AE1-9A8B-32D1C0EDC654}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{7C6E923C-41B4-47AB-8189-E2120E1C4FCB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{4C55F244-FC3E-4AD1-BEA9-0CB8797146E0}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{17E0CF7B-435D-420A-BEF8-1B00B1793EC6}"/>
   </bookViews>
   <sheets>
     <sheet name="grid_links" sheetId="1" r:id="rId1"/>
@@ -1018,7 +1018,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FD6C26F8-5C83-475B-86E3-FC922022288C}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FE699A14-1C5F-4B2B-A632-B8A4C9F2D2B5}">
   <dimension ref="B3:L69"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>

--- a/VerveStacks_POL_grids_syn_5/SuppXLS/trades/scentrade__trade_links.xlsx
+++ b/VerveStacks_POL_grids_syn_5/SuppXLS/trades/scentrade__trade_links.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_POL_grids_syn_5\SuppXLS\trades\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{7C6E923C-41B4-47AB-8189-E2120E1C4FCB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{1F1F89F5-B22C-4112-B4D8-76042174A223}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{17E0CF7B-435D-420A-BEF8-1B00B1793EC6}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{1A0AF5CD-0E14-41EE-AE86-627C7D3CA385}"/>
   </bookViews>
   <sheets>
     <sheet name="grid_links" sheetId="1" r:id="rId1"/>
@@ -1018,7 +1018,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FE699A14-1C5F-4B2B-A632-B8A4C9F2D2B5}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E4678F5E-71CE-497C-8BAD-872058FA60BD}">
   <dimension ref="B3:L69"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>

--- a/VerveStacks_POL_grids_syn_5/SuppXLS/trades/scentrade__trade_links.xlsx
+++ b/VerveStacks_POL_grids_syn_5/SuppXLS/trades/scentrade__trade_links.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_POL_grids_syn_5\SuppXLS\trades\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{1F1F89F5-B22C-4112-B4D8-76042174A223}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{82FB81CC-E12A-4695-8381-533DE9A20F1D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{1A0AF5CD-0E14-41EE-AE86-627C7D3CA385}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{72EED2A6-0D28-44A6-A5EC-094DDCC1C001}"/>
   </bookViews>
   <sheets>
     <sheet name="grid_links" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="596" uniqueCount="204">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="362" uniqueCount="126">
   <si>
     <t>~tradelinks_dins</t>
   </si>
@@ -101,25 +101,34 @@
     <t>e_gen0</t>
   </si>
   <si>
-    <t>g_gen0-dem0</t>
+    <t>g_gen0-dem3</t>
+  </si>
+  <si>
+    <t>g_gen0-dem4</t>
   </si>
   <si>
     <t>e_gen1</t>
   </si>
   <si>
+    <t>g_gen1-dem0</t>
+  </si>
+  <si>
     <t>g_gen1-dem1</t>
   </si>
   <si>
     <t>g_gen1-dem2</t>
   </si>
   <si>
+    <t>g_gen1-dem4</t>
+  </si>
+  <si>
     <t>e_gen2</t>
   </si>
   <si>
-    <t>g_gen2-dem3</t>
-  </si>
-  <si>
-    <t>g_gen2-dem4</t>
+    <t>g_gen2-dem1</t>
+  </si>
+  <si>
+    <t>g_gen2-dem2</t>
   </si>
   <si>
     <t>e_gen3</t>
@@ -137,15 +146,6 @@
     <t>g_gen4-dem0</t>
   </si>
   <si>
-    <t>g_gen4-dem1</t>
-  </si>
-  <si>
-    <t>g_gen4-dem2</t>
-  </si>
-  <si>
-    <t>g_gen4-dem4</t>
-  </si>
-  <si>
     <t>e_sol1</t>
   </si>
   <si>
@@ -185,19 +185,19 @@
     <t>e_sol15</t>
   </si>
   <si>
-    <t>g_sol15-gen1</t>
+    <t>g_sol15-gen2</t>
   </si>
   <si>
     <t>e_sol16</t>
   </si>
   <si>
-    <t>g_sol16-gen4</t>
+    <t>g_sol16-gen1</t>
   </si>
   <si>
     <t>e_sol17</t>
   </si>
   <si>
-    <t>g_sol17-gen4</t>
+    <t>g_sol17-gen1</t>
   </si>
   <si>
     <t>e_sol18</t>
@@ -209,13 +209,13 @@
     <t>e_sol19</t>
   </si>
   <si>
-    <t>g_sol19-gen2</t>
+    <t>g_sol19-gen0</t>
   </si>
   <si>
     <t>e_sol2</t>
   </si>
   <si>
-    <t>g_sol2-gen1</t>
+    <t>g_sol2-gen2</t>
   </si>
   <si>
     <t>e_sol3</t>
@@ -245,7 +245,7 @@
     <t>e_sol7</t>
   </si>
   <si>
-    <t>g_sol7-gen0</t>
+    <t>g_sol7-gen4</t>
   </si>
   <si>
     <t>e_sol8</t>
@@ -260,94 +260,10 @@
     <t>g_sol9-dem4</t>
   </si>
   <si>
-    <t>e_wof0</t>
-  </si>
-  <si>
-    <t>g_wof0-gen1</t>
-  </si>
-  <si>
-    <t>e_wof1</t>
-  </si>
-  <si>
-    <t>g_wof1-dem0</t>
-  </si>
-  <si>
-    <t>e_wof10</t>
-  </si>
-  <si>
-    <t>g_wof10-gen0</t>
-  </si>
-  <si>
-    <t>e_wof2</t>
-  </si>
-  <si>
-    <t>g_wof2-gen0</t>
-  </si>
-  <si>
-    <t>e_wof3</t>
-  </si>
-  <si>
-    <t>g_wof3-dem0</t>
-  </si>
-  <si>
-    <t>e_wof4</t>
-  </si>
-  <si>
-    <t>g_wof4-gen0</t>
-  </si>
-  <si>
-    <t>e_wof5</t>
-  </si>
-  <si>
-    <t>g_wof5-gen0</t>
-  </si>
-  <si>
-    <t>e_wof6</t>
-  </si>
-  <si>
-    <t>g_wof6-gen0</t>
-  </si>
-  <si>
-    <t>e_wof7</t>
-  </si>
-  <si>
-    <t>g_wof7-gen3</t>
-  </si>
-  <si>
-    <t>e_wof8</t>
-  </si>
-  <si>
-    <t>g_wof8-gen0</t>
-  </si>
-  <si>
-    <t>e_wof9</t>
-  </si>
-  <si>
-    <t>g_wof9-gen0</t>
-  </si>
-  <si>
     <t>e_won0</t>
   </si>
   <si>
-    <t>g_won0-gen2</t>
-  </si>
-  <si>
-    <t>e_won1</t>
-  </si>
-  <si>
-    <t>g_won1-gen2</t>
-  </si>
-  <si>
-    <t>e_won10</t>
-  </si>
-  <si>
-    <t>g_won10-gen0</t>
-  </si>
-  <si>
-    <t>e_won11</t>
-  </si>
-  <si>
-    <t>g_won11-dem2</t>
+    <t>g_won0-gen0</t>
   </si>
   <si>
     <t>e_won12</t>
@@ -362,84 +278,12 @@
     <t>g_won13-dem2</t>
   </si>
   <si>
-    <t>e_won14</t>
-  </si>
-  <si>
-    <t>g_won14-dem2</t>
-  </si>
-  <si>
-    <t>e_won15</t>
-  </si>
-  <si>
-    <t>g_won15-dem1</t>
-  </si>
-  <si>
-    <t>e_won16</t>
-  </si>
-  <si>
-    <t>g_won16-dem3</t>
-  </si>
-  <si>
-    <t>e_won17</t>
-  </si>
-  <si>
-    <t>g_won17-dem3</t>
-  </si>
-  <si>
     <t>e_won18</t>
   </si>
   <si>
     <t>g_won18-dem2</t>
   </si>
   <si>
-    <t>e_won19</t>
-  </si>
-  <si>
-    <t>g_won19-dem1</t>
-  </si>
-  <si>
-    <t>e_won2</t>
-  </si>
-  <si>
-    <t>g_won2-dem3</t>
-  </si>
-  <si>
-    <t>e_won3</t>
-  </si>
-  <si>
-    <t>g_won3-dem4</t>
-  </si>
-  <si>
-    <t>e_won4</t>
-  </si>
-  <si>
-    <t>g_won4-dem3</t>
-  </si>
-  <si>
-    <t>e_won5</t>
-  </si>
-  <si>
-    <t>g_won5-dem4</t>
-  </si>
-  <si>
-    <t>e_won6</t>
-  </si>
-  <si>
-    <t>g_won6-gen4</t>
-  </si>
-  <si>
-    <t>e_won7</t>
-  </si>
-  <si>
-    <t>g_won7-dem4</t>
-  </si>
-  <si>
-    <t>e_won8</t>
-  </si>
-  <si>
-    <t>g_won8-dem0</t>
-  </si>
-  <si>
     <t>e_won9</t>
   </si>
   <si>
@@ -467,37 +311,37 @@
     <t>grid link -240.0 km- Demand cluster 2 to Demand cluster 0</t>
   </si>
   <si>
-    <t>grid link -167.0 km- Generation cluster 0 to Demand cluster 0</t>
-  </si>
-  <si>
-    <t>grid link -22.0 km- Generation cluster 1 to Demand cluster 1</t>
-  </si>
-  <si>
-    <t>grid link -247.0 km- Generation cluster 1 to Demand cluster 2</t>
-  </si>
-  <si>
-    <t>grid link -108.0 km- Generation cluster 2 to Demand cluster 3</t>
-  </si>
-  <si>
-    <t>grid link -101.0 km- Generation cluster 2 to Demand cluster 4</t>
+    <t>grid link -99.0 km- Generation cluster 0 to Demand cluster 3</t>
+  </si>
+  <si>
+    <t>grid link -109.0 km- Generation cluster 0 to Demand cluster 4</t>
+  </si>
+  <si>
+    <t>grid link -116.0 km- Generation cluster 1 to Demand cluster 0</t>
+  </si>
+  <si>
+    <t>grid link -242.0 km- Generation cluster 1 to Demand cluster 1</t>
+  </si>
+  <si>
+    <t>grid link -185.0 km- Generation cluster 1 to Demand cluster 2</t>
+  </si>
+  <si>
+    <t>grid link -171.0 km- Generation cluster 1 to Demand cluster 4</t>
+  </si>
+  <si>
+    <t>grid link -27.0 km- Generation cluster 2 to Demand cluster 1</t>
+  </si>
+  <si>
+    <t>grid link -243.0 km- Generation cluster 2 to Demand cluster 2</t>
   </si>
   <si>
     <t>grid link -225.0 km- Generation cluster 3 to Demand cluster 0</t>
   </si>
   <si>
-    <t>grid link -129.0 km- Generation cluster 3 to Demand cluster 2</t>
-  </si>
-  <si>
-    <t>grid link -122.0 km- Generation cluster 4 to Demand cluster 0</t>
-  </si>
-  <si>
-    <t>grid link -235.0 km- Generation cluster 4 to Demand cluster 1</t>
-  </si>
-  <si>
-    <t>grid link -184.0 km- Generation cluster 4 to Demand cluster 2</t>
-  </si>
-  <si>
-    <t>grid link -169.0 km- Generation cluster 4 to Demand cluster 4</t>
+    <t>grid link -130.0 km- Generation cluster 3 to Demand cluster 2</t>
+  </si>
+  <si>
+    <t>grid link -169.0 km- Generation cluster 4 to Demand cluster 0</t>
   </si>
   <si>
     <t>grid link -109.0 km- Renewable cluster 1 to Demand cluster 2</t>
@@ -518,22 +362,22 @@
     <t>grid link -92.0 km- Renewable cluster 14 to Demand cluster 1</t>
   </si>
   <si>
-    <t>grid link -27.0 km- Potential connection: Renewable cluster 15 to Generation cluster 1</t>
-  </si>
-  <si>
-    <t>grid link -67.0 km- Potential connection: Renewable cluster 16 to Generation cluster 4</t>
-  </si>
-  <si>
-    <t>grid link -22.0 km- Potential connection: Renewable cluster 17 to Generation cluster 4</t>
+    <t>grid link -29.0 km- Potential connection: Renewable cluster 15 to Generation cluster 2</t>
+  </si>
+  <si>
+    <t>grid link -73.0 km- Potential connection: Renewable cluster 16 to Generation cluster 1</t>
+  </si>
+  <si>
+    <t>grid link -17.0 km- Potential connection: Renewable cluster 17 to Generation cluster 1</t>
   </si>
   <si>
     <t>grid link -19.0 km- Potential connection: Renewable cluster 18 to Demand cluster 4</t>
   </si>
   <si>
-    <t>grid link -83.0 km- Potential connection: Renewable cluster 19 to Generation cluster 2</t>
-  </si>
-  <si>
-    <t>grid link -151.0 km- Potential connection: Renewable cluster 2 to Generation cluster 1</t>
+    <t>grid link -75.0 km- Potential connection: Renewable cluster 19 to Generation cluster 0</t>
+  </si>
+  <si>
+    <t>grid link -147.0 km- Potential connection: Renewable cluster 2 to Generation cluster 2</t>
   </si>
   <si>
     <t>grid link -85.0 km- Renewable cluster 3 to Demand cluster 2</t>
@@ -548,7 +392,7 @@
     <t>grid link -139.0 km- Potential connection: Renewable cluster 6 to Demand cluster 0</t>
   </si>
   <si>
-    <t>grid link -95.0 km- Potential connection: Renewable cluster 7 to Generation cluster 0</t>
+    <t>grid link -96.0 km- Potential connection: Renewable cluster 7 to Generation cluster 4</t>
   </si>
   <si>
     <t>grid link -32.0 km- Potential connection: Renewable cluster 8 to Demand cluster 0</t>
@@ -557,97 +401,19 @@
     <t>grid link -116.0 km- Potential connection: Renewable cluster 9 to Demand cluster 4</t>
   </si>
   <si>
-    <t>grid link -45.0 km- Potential connection: Renewable cluster 40 to Generation cluster 1</t>
-  </si>
-  <si>
-    <t>grid link -74.0 km- Potential connection: Renewable cluster 41 to Demand cluster 0</t>
-  </si>
-  <si>
-    <t>grid link -88.0 km- Potential connection: Renewable cluster 50 to Generation cluster 0</t>
-  </si>
-  <si>
-    <t>grid link -117.0 km- Potential connection: Renewable cluster 42 to Generation cluster 0</t>
-  </si>
-  <si>
-    <t>grid link -116.0 km- Potential connection: Renewable cluster 43 to Demand cluster 0</t>
-  </si>
-  <si>
-    <t>grid link -67.0 km- Potential connection: Renewable cluster 44 to Generation cluster 0</t>
-  </si>
-  <si>
-    <t>grid link -96.0 km- Potential connection: Renewable cluster 45 to Generation cluster 0</t>
-  </si>
-  <si>
-    <t>grid link -35.0 km- Potential connection: Renewable cluster 46 to Generation cluster 0</t>
-  </si>
-  <si>
-    <t>grid link -126.0 km- Potential connection: Renewable cluster 47 to Generation cluster 3</t>
-  </si>
-  <si>
-    <t>grid link -134.0 km- Potential connection: Renewable cluster 48 to Generation cluster 0</t>
-  </si>
-  <si>
-    <t>grid link -67.0 km- Potential connection: Renewable cluster 49 to Generation cluster 0</t>
-  </si>
-  <si>
-    <t>grid link -34.0 km- Potential connection: Renewable cluster 20 to Generation cluster 2</t>
-  </si>
-  <si>
-    <t>grid link -94.0 km- Potential connection: Renewable cluster 21 to Generation cluster 2</t>
-  </si>
-  <si>
-    <t>grid link -118.0 km- Potential connection: Renewable cluster 30 to Generation cluster 0</t>
-  </si>
-  <si>
-    <t>grid link -113.0 km- Potential connection: Renewable cluster 31 to Demand cluster 2</t>
-  </si>
-  <si>
-    <t>grid link -94.0 km- Renewable cluster 32 to Demand cluster 2</t>
-  </si>
-  <si>
-    <t>grid link -71.0 km- Renewable cluster 33 to Demand cluster 2</t>
-  </si>
-  <si>
-    <t>grid link -99.0 km- Potential connection: Renewable cluster 34 to Demand cluster 2</t>
-  </si>
-  <si>
-    <t>grid link -131.0 km- Potential connection: Renewable cluster 35 to Demand cluster 1</t>
-  </si>
-  <si>
-    <t>grid link -145.0 km- Potential connection: Renewable cluster 36 to Demand cluster 3</t>
-  </si>
-  <si>
-    <t>grid link -123.0 km- Potential connection: Renewable cluster 37 to Demand cluster 3</t>
-  </si>
-  <si>
-    <t>grid link -199.0 km- Renewable cluster 38 to Demand cluster 2</t>
-  </si>
-  <si>
-    <t>grid link -48.0 km- Potential connection: Renewable cluster 39 to Demand cluster 1</t>
-  </si>
-  <si>
-    <t>grid link -52.0 km- Potential connection: Renewable cluster 22 to Demand cluster 3</t>
-  </si>
-  <si>
-    <t>grid link -68.0 km- Potential connection: Renewable cluster 23 to Demand cluster 4</t>
-  </si>
-  <si>
-    <t>grid link -121.0 km- Potential connection: Renewable cluster 24 to Demand cluster 3</t>
-  </si>
-  <si>
-    <t>grid link -159.0 km- Potential connection: Renewable cluster 25 to Demand cluster 4</t>
-  </si>
-  <si>
-    <t>grid link -24.0 km- Potential connection: Renewable cluster 26 to Generation cluster 4</t>
-  </si>
-  <si>
-    <t>grid link -77.0 km- Potential connection: Renewable cluster 27 to Demand cluster 4</t>
-  </si>
-  <si>
-    <t>grid link -176.0 km- Potential connection: Renewable cluster 28 to Demand cluster 0</t>
-  </si>
-  <si>
-    <t>grid link -38.0 km- Renewable cluster 29 to Demand cluster 0</t>
+    <t>grid link -43.0 km- Potential connection: Renewable cluster 20 to Generation cluster 0</t>
+  </si>
+  <si>
+    <t>grid link -0.0 km- Renewable cluster 32 to Demand cluster 2</t>
+  </si>
+  <si>
+    <t>grid link -0.0 km- Renewable cluster 33 to Demand cluster 2</t>
+  </si>
+  <si>
+    <t>grid link -0.0 km- Renewable cluster 38 to Demand cluster 2</t>
+  </si>
+  <si>
+    <t>grid link -0.0 km- Renewable cluster 29 to Demand cluster 0</t>
   </si>
 </sst>
 </file>
@@ -1018,8 +784,8 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E4678F5E-71CE-497C-8BAD-872058FA60BD}">
-  <dimension ref="B3:L69"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E67131D7-2E3D-464C-9B01-C0892CEA7633}">
+  <dimension ref="B3:L43"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
     <row r="3" spans="2:12" x14ac:dyDescent="0.45">
@@ -1027,7 +793,7 @@
         <v>0</v>
       </c>
       <c r="K3" t="s">
-        <v>136</v>
+        <v>84</v>
       </c>
     </row>
     <row r="4" spans="2:12" x14ac:dyDescent="0.45">
@@ -1053,10 +819,10 @@
         <v>7</v>
       </c>
       <c r="K4" t="s">
-        <v>137</v>
+        <v>85</v>
       </c>
       <c r="L4" t="s">
-        <v>138</v>
+        <v>86</v>
       </c>
     </row>
     <row r="5" spans="2:12" x14ac:dyDescent="0.45">
@@ -1085,7 +851,7 @@
         <v>12</v>
       </c>
       <c r="L5" t="s">
-        <v>139</v>
+        <v>87</v>
       </c>
     </row>
     <row r="6" spans="2:12" x14ac:dyDescent="0.45">
@@ -1114,7 +880,7 @@
         <v>15</v>
       </c>
       <c r="L6" t="s">
-        <v>140</v>
+        <v>88</v>
       </c>
     </row>
     <row r="7" spans="2:12" x14ac:dyDescent="0.45">
@@ -1143,7 +909,7 @@
         <v>17</v>
       </c>
       <c r="L7" t="s">
-        <v>141</v>
+        <v>89</v>
       </c>
     </row>
     <row r="8" spans="2:12" x14ac:dyDescent="0.45">
@@ -1172,7 +938,7 @@
         <v>19</v>
       </c>
       <c r="L8" t="s">
-        <v>142</v>
+        <v>90</v>
       </c>
     </row>
     <row r="9" spans="2:12" x14ac:dyDescent="0.45">
@@ -1189,7 +955,7 @@
         <v>20</v>
       </c>
       <c r="F9" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="G9" t="s">
         <v>21</v>
@@ -1201,7 +967,7 @@
         <v>21</v>
       </c>
       <c r="L9" t="s">
-        <v>143</v>
+        <v>91</v>
       </c>
     </row>
     <row r="10" spans="2:12" x14ac:dyDescent="0.45">
@@ -1215,22 +981,22 @@
         <v>9</v>
       </c>
       <c r="E10" t="s">
+        <v>20</v>
+      </c>
+      <c r="F10" t="s">
+        <v>16</v>
+      </c>
+      <c r="G10" t="s">
         <v>22</v>
       </c>
-      <c r="F10" t="s">
-        <v>10</v>
-      </c>
-      <c r="G10" t="s">
-        <v>23</v>
-      </c>
       <c r="H10" t="s">
         <v>13</v>
       </c>
       <c r="K10" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="L10" t="s">
-        <v>144</v>
+        <v>92</v>
       </c>
     </row>
     <row r="11" spans="2:12" x14ac:dyDescent="0.45">
@@ -1244,10 +1010,10 @@
         <v>9</v>
       </c>
       <c r="E11" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="F11" t="s">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="G11" t="s">
         <v>24</v>
@@ -1259,7 +1025,7 @@
         <v>24</v>
       </c>
       <c r="L11" t="s">
-        <v>145</v>
+        <v>93</v>
       </c>
     </row>
     <row r="12" spans="2:12" x14ac:dyDescent="0.45">
@@ -1273,22 +1039,22 @@
         <v>9</v>
       </c>
       <c r="E12" t="s">
+        <v>23</v>
+      </c>
+      <c r="F12" t="s">
+        <v>10</v>
+      </c>
+      <c r="G12" t="s">
         <v>25</v>
       </c>
-      <c r="F12" t="s">
-        <v>14</v>
-      </c>
-      <c r="G12" t="s">
-        <v>26</v>
-      </c>
       <c r="H12" t="s">
         <v>13</v>
       </c>
       <c r="K12" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="L12" t="s">
-        <v>146</v>
+        <v>94</v>
       </c>
     </row>
     <row r="13" spans="2:12" x14ac:dyDescent="0.45">
@@ -1302,22 +1068,22 @@
         <v>9</v>
       </c>
       <c r="E13" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="F13" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="G13" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="H13" t="s">
         <v>13</v>
       </c>
       <c r="K13" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="L13" t="s">
-        <v>147</v>
+        <v>95</v>
       </c>
     </row>
     <row r="14" spans="2:12" x14ac:dyDescent="0.45">
@@ -1331,22 +1097,22 @@
         <v>9</v>
       </c>
       <c r="E14" t="s">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="F14" t="s">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="G14" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="H14" t="s">
         <v>13</v>
       </c>
       <c r="K14" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="L14" t="s">
-        <v>148</v>
+        <v>96</v>
       </c>
     </row>
     <row r="15" spans="2:12" x14ac:dyDescent="0.45">
@@ -1363,19 +1129,19 @@
         <v>28</v>
       </c>
       <c r="F15" t="s">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="G15" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="H15" t="s">
         <v>13</v>
       </c>
       <c r="K15" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="L15" t="s">
-        <v>149</v>
+        <v>97</v>
       </c>
     </row>
     <row r="16" spans="2:12" x14ac:dyDescent="0.45">
@@ -1389,22 +1155,22 @@
         <v>9</v>
       </c>
       <c r="E16" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="F16" t="s">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="G16" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="H16" t="s">
         <v>13</v>
       </c>
       <c r="K16" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="L16" t="s">
-        <v>150</v>
+        <v>98</v>
       </c>
     </row>
     <row r="17" spans="2:12" x14ac:dyDescent="0.45">
@@ -1421,19 +1187,19 @@
         <v>31</v>
       </c>
       <c r="F17" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G17" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="H17" t="s">
         <v>13</v>
       </c>
       <c r="K17" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="L17" t="s">
-        <v>151</v>
+        <v>99</v>
       </c>
     </row>
     <row r="18" spans="2:12" x14ac:dyDescent="0.45">
@@ -1453,16 +1219,16 @@
         <v>18</v>
       </c>
       <c r="G18" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="H18" t="s">
         <v>13</v>
       </c>
       <c r="K18" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="L18" t="s">
-        <v>152</v>
+        <v>100</v>
       </c>
     </row>
     <row r="19" spans="2:12" x14ac:dyDescent="0.45">
@@ -1476,10 +1242,10 @@
         <v>9</v>
       </c>
       <c r="E19" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="F19" t="s">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="G19" t="s">
         <v>35</v>
@@ -1491,7 +1257,7 @@
         <v>35</v>
       </c>
       <c r="L19" t="s">
-        <v>153</v>
+        <v>101</v>
       </c>
     </row>
     <row r="20" spans="2:12" x14ac:dyDescent="0.45">
@@ -1520,7 +1286,7 @@
         <v>37</v>
       </c>
       <c r="L20" t="s">
-        <v>154</v>
+        <v>102</v>
       </c>
     </row>
     <row r="21" spans="2:12" x14ac:dyDescent="0.45">
@@ -1549,7 +1315,7 @@
         <v>39</v>
       </c>
       <c r="L21" t="s">
-        <v>155</v>
+        <v>103</v>
       </c>
     </row>
     <row r="22" spans="2:12" x14ac:dyDescent="0.45">
@@ -1578,7 +1344,7 @@
         <v>41</v>
       </c>
       <c r="L22" t="s">
-        <v>156</v>
+        <v>104</v>
       </c>
     </row>
     <row r="23" spans="2:12" x14ac:dyDescent="0.45">
@@ -1607,7 +1373,7 @@
         <v>43</v>
       </c>
       <c r="L23" t="s">
-        <v>157</v>
+        <v>105</v>
       </c>
     </row>
     <row r="24" spans="2:12" x14ac:dyDescent="0.45">
@@ -1636,7 +1402,7 @@
         <v>45</v>
       </c>
       <c r="L24" t="s">
-        <v>158</v>
+        <v>106</v>
       </c>
     </row>
     <row r="25" spans="2:12" x14ac:dyDescent="0.45">
@@ -1665,7 +1431,7 @@
         <v>47</v>
       </c>
       <c r="L25" t="s">
-        <v>159</v>
+        <v>107</v>
       </c>
     </row>
     <row r="26" spans="2:12" x14ac:dyDescent="0.45">
@@ -1682,7 +1448,7 @@
         <v>48</v>
       </c>
       <c r="F26" t="s">
-        <v>22</v>
+        <v>28</v>
       </c>
       <c r="G26" t="s">
         <v>49</v>
@@ -1694,7 +1460,7 @@
         <v>49</v>
       </c>
       <c r="L26" t="s">
-        <v>160</v>
+        <v>108</v>
       </c>
     </row>
     <row r="27" spans="2:12" x14ac:dyDescent="0.45">
@@ -1711,7 +1477,7 @@
         <v>50</v>
       </c>
       <c r="F27" t="s">
-        <v>31</v>
+        <v>23</v>
       </c>
       <c r="G27" t="s">
         <v>51</v>
@@ -1723,7 +1489,7 @@
         <v>51</v>
       </c>
       <c r="L27" t="s">
-        <v>161</v>
+        <v>109</v>
       </c>
     </row>
     <row r="28" spans="2:12" x14ac:dyDescent="0.45">
@@ -1740,7 +1506,7 @@
         <v>52</v>
       </c>
       <c r="F28" t="s">
-        <v>31</v>
+        <v>23</v>
       </c>
       <c r="G28" t="s">
         <v>53</v>
@@ -1752,7 +1518,7 @@
         <v>53</v>
       </c>
       <c r="L28" t="s">
-        <v>162</v>
+        <v>110</v>
       </c>
     </row>
     <row r="29" spans="2:12" x14ac:dyDescent="0.45">
@@ -1781,7 +1547,7 @@
         <v>55</v>
       </c>
       <c r="L29" t="s">
-        <v>163</v>
+        <v>111</v>
       </c>
     </row>
     <row r="30" spans="2:12" x14ac:dyDescent="0.45">
@@ -1798,7 +1564,7 @@
         <v>56</v>
       </c>
       <c r="F30" t="s">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="G30" t="s">
         <v>57</v>
@@ -1810,7 +1576,7 @@
         <v>57</v>
       </c>
       <c r="L30" t="s">
-        <v>164</v>
+        <v>112</v>
       </c>
     </row>
     <row r="31" spans="2:12" x14ac:dyDescent="0.45">
@@ -1827,7 +1593,7 @@
         <v>58</v>
       </c>
       <c r="F31" t="s">
-        <v>22</v>
+        <v>28</v>
       </c>
       <c r="G31" t="s">
         <v>59</v>
@@ -1839,7 +1605,7 @@
         <v>59</v>
       </c>
       <c r="L31" t="s">
-        <v>165</v>
+        <v>113</v>
       </c>
     </row>
     <row r="32" spans="2:12" x14ac:dyDescent="0.45">
@@ -1868,7 +1634,7 @@
         <v>61</v>
       </c>
       <c r="L32" t="s">
-        <v>166</v>
+        <v>114</v>
       </c>
     </row>
     <row r="33" spans="2:12" x14ac:dyDescent="0.45">
@@ -1885,7 +1651,7 @@
         <v>62</v>
       </c>
       <c r="F33" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="G33" t="s">
         <v>63</v>
@@ -1897,7 +1663,7 @@
         <v>63</v>
       </c>
       <c r="L33" t="s">
-        <v>167</v>
+        <v>115</v>
       </c>
     </row>
     <row r="34" spans="2:12" x14ac:dyDescent="0.45">
@@ -1926,7 +1692,7 @@
         <v>65</v>
       </c>
       <c r="L34" t="s">
-        <v>168</v>
+        <v>116</v>
       </c>
     </row>
     <row r="35" spans="2:12" x14ac:dyDescent="0.45">
@@ -1955,7 +1721,7 @@
         <v>67</v>
       </c>
       <c r="L35" t="s">
-        <v>169</v>
+        <v>117</v>
       </c>
     </row>
     <row r="36" spans="2:12" x14ac:dyDescent="0.45">
@@ -1972,7 +1738,7 @@
         <v>68</v>
       </c>
       <c r="F36" t="s">
-        <v>20</v>
+        <v>34</v>
       </c>
       <c r="G36" t="s">
         <v>69</v>
@@ -1984,7 +1750,7 @@
         <v>69</v>
       </c>
       <c r="L36" t="s">
-        <v>170</v>
+        <v>118</v>
       </c>
     </row>
     <row r="37" spans="2:12" x14ac:dyDescent="0.45">
@@ -2013,7 +1779,7 @@
         <v>71</v>
       </c>
       <c r="L37" t="s">
-        <v>171</v>
+        <v>119</v>
       </c>
     </row>
     <row r="38" spans="2:12" x14ac:dyDescent="0.45">
@@ -2042,7 +1808,7 @@
         <v>73</v>
       </c>
       <c r="L38" t="s">
-        <v>172</v>
+        <v>120</v>
       </c>
     </row>
     <row r="39" spans="2:12" x14ac:dyDescent="0.45">
@@ -2059,7 +1825,7 @@
         <v>74</v>
       </c>
       <c r="F39" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="G39" t="s">
         <v>75</v>
@@ -2071,7 +1837,7 @@
         <v>75</v>
       </c>
       <c r="L39" t="s">
-        <v>173</v>
+        <v>121</v>
       </c>
     </row>
     <row r="40" spans="2:12" x14ac:dyDescent="0.45">
@@ -2088,7 +1854,7 @@
         <v>76</v>
       </c>
       <c r="F40" t="s">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="G40" t="s">
         <v>77</v>
@@ -2100,7 +1866,7 @@
         <v>77</v>
       </c>
       <c r="L40" t="s">
-        <v>174</v>
+        <v>122</v>
       </c>
     </row>
     <row r="41" spans="2:12" x14ac:dyDescent="0.45">
@@ -2117,7 +1883,7 @@
         <v>78</v>
       </c>
       <c r="F41" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="G41" t="s">
         <v>79</v>
@@ -2129,7 +1895,7 @@
         <v>79</v>
       </c>
       <c r="L41" t="s">
-        <v>175</v>
+        <v>123</v>
       </c>
     </row>
     <row r="42" spans="2:12" x14ac:dyDescent="0.45">
@@ -2146,7 +1912,7 @@
         <v>80</v>
       </c>
       <c r="F42" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="G42" t="s">
         <v>81</v>
@@ -2158,7 +1924,7 @@
         <v>81</v>
       </c>
       <c r="L42" t="s">
-        <v>176</v>
+        <v>124</v>
       </c>
     </row>
     <row r="43" spans="2:12" x14ac:dyDescent="0.45">
@@ -2187,761 +1953,7 @@
         <v>83</v>
       </c>
       <c r="L43" t="s">
-        <v>177</v>
-      </c>
-    </row>
-    <row r="44" spans="2:12" x14ac:dyDescent="0.45">
-      <c r="B44" t="s">
-        <v>8</v>
-      </c>
-      <c r="C44" t="s">
-        <v>8</v>
-      </c>
-      <c r="D44" t="s">
-        <v>9</v>
-      </c>
-      <c r="E44" t="s">
-        <v>84</v>
-      </c>
-      <c r="F44" t="s">
-        <v>20</v>
-      </c>
-      <c r="G44" t="s">
-        <v>85</v>
-      </c>
-      <c r="H44" t="s">
-        <v>13</v>
-      </c>
-      <c r="K44" t="s">
-        <v>85</v>
-      </c>
-      <c r="L44" t="s">
-        <v>178</v>
-      </c>
-    </row>
-    <row r="45" spans="2:12" x14ac:dyDescent="0.45">
-      <c r="B45" t="s">
-        <v>8</v>
-      </c>
-      <c r="C45" t="s">
-        <v>8</v>
-      </c>
-      <c r="D45" t="s">
-        <v>9</v>
-      </c>
-      <c r="E45" t="s">
-        <v>86</v>
-      </c>
-      <c r="F45" t="s">
-        <v>20</v>
-      </c>
-      <c r="G45" t="s">
-        <v>87</v>
-      </c>
-      <c r="H45" t="s">
-        <v>13</v>
-      </c>
-      <c r="K45" t="s">
-        <v>87</v>
-      </c>
-      <c r="L45" t="s">
-        <v>179</v>
-      </c>
-    </row>
-    <row r="46" spans="2:12" x14ac:dyDescent="0.45">
-      <c r="B46" t="s">
-        <v>8</v>
-      </c>
-      <c r="C46" t="s">
-        <v>8</v>
-      </c>
-      <c r="D46" t="s">
-        <v>9</v>
-      </c>
-      <c r="E46" t="s">
-        <v>88</v>
-      </c>
-      <c r="F46" t="s">
-        <v>20</v>
-      </c>
-      <c r="G46" t="s">
-        <v>89</v>
-      </c>
-      <c r="H46" t="s">
-        <v>13</v>
-      </c>
-      <c r="K46" t="s">
-        <v>89</v>
-      </c>
-      <c r="L46" t="s">
-        <v>180</v>
-      </c>
-    </row>
-    <row r="47" spans="2:12" x14ac:dyDescent="0.45">
-      <c r="B47" t="s">
-        <v>8</v>
-      </c>
-      <c r="C47" t="s">
-        <v>8</v>
-      </c>
-      <c r="D47" t="s">
-        <v>9</v>
-      </c>
-      <c r="E47" t="s">
-        <v>90</v>
-      </c>
-      <c r="F47" t="s">
-        <v>28</v>
-      </c>
-      <c r="G47" t="s">
-        <v>91</v>
-      </c>
-      <c r="H47" t="s">
-        <v>13</v>
-      </c>
-      <c r="K47" t="s">
-        <v>91</v>
-      </c>
-      <c r="L47" t="s">
-        <v>181</v>
-      </c>
-    </row>
-    <row r="48" spans="2:12" x14ac:dyDescent="0.45">
-      <c r="B48" t="s">
-        <v>8</v>
-      </c>
-      <c r="C48" t="s">
-        <v>8</v>
-      </c>
-      <c r="D48" t="s">
-        <v>9</v>
-      </c>
-      <c r="E48" t="s">
-        <v>92</v>
-      </c>
-      <c r="F48" t="s">
-        <v>20</v>
-      </c>
-      <c r="G48" t="s">
-        <v>93</v>
-      </c>
-      <c r="H48" t="s">
-        <v>13</v>
-      </c>
-      <c r="K48" t="s">
-        <v>93</v>
-      </c>
-      <c r="L48" t="s">
-        <v>182</v>
-      </c>
-    </row>
-    <row r="49" spans="2:12" x14ac:dyDescent="0.45">
-      <c r="B49" t="s">
-        <v>8</v>
-      </c>
-      <c r="C49" t="s">
-        <v>8</v>
-      </c>
-      <c r="D49" t="s">
-        <v>9</v>
-      </c>
-      <c r="E49" t="s">
-        <v>94</v>
-      </c>
-      <c r="F49" t="s">
-        <v>20</v>
-      </c>
-      <c r="G49" t="s">
-        <v>95</v>
-      </c>
-      <c r="H49" t="s">
-        <v>13</v>
-      </c>
-      <c r="K49" t="s">
-        <v>95</v>
-      </c>
-      <c r="L49" t="s">
-        <v>183</v>
-      </c>
-    </row>
-    <row r="50" spans="2:12" x14ac:dyDescent="0.45">
-      <c r="B50" t="s">
-        <v>8</v>
-      </c>
-      <c r="C50" t="s">
-        <v>8</v>
-      </c>
-      <c r="D50" t="s">
-        <v>9</v>
-      </c>
-      <c r="E50" t="s">
-        <v>96</v>
-      </c>
-      <c r="F50" t="s">
-        <v>25</v>
-      </c>
-      <c r="G50" t="s">
-        <v>97</v>
-      </c>
-      <c r="H50" t="s">
-        <v>13</v>
-      </c>
-      <c r="K50" t="s">
-        <v>97</v>
-      </c>
-      <c r="L50" t="s">
-        <v>184</v>
-      </c>
-    </row>
-    <row r="51" spans="2:12" x14ac:dyDescent="0.45">
-      <c r="B51" t="s">
-        <v>8</v>
-      </c>
-      <c r="C51" t="s">
-        <v>8</v>
-      </c>
-      <c r="D51" t="s">
-        <v>9</v>
-      </c>
-      <c r="E51" t="s">
-        <v>98</v>
-      </c>
-      <c r="F51" t="s">
-        <v>25</v>
-      </c>
-      <c r="G51" t="s">
-        <v>99</v>
-      </c>
-      <c r="H51" t="s">
-        <v>13</v>
-      </c>
-      <c r="K51" t="s">
-        <v>99</v>
-      </c>
-      <c r="L51" t="s">
-        <v>185</v>
-      </c>
-    </row>
-    <row r="52" spans="2:12" x14ac:dyDescent="0.45">
-      <c r="B52" t="s">
-        <v>8</v>
-      </c>
-      <c r="C52" t="s">
-        <v>8</v>
-      </c>
-      <c r="D52" t="s">
-        <v>9</v>
-      </c>
-      <c r="E52" t="s">
-        <v>100</v>
-      </c>
-      <c r="F52" t="s">
-        <v>20</v>
-      </c>
-      <c r="G52" t="s">
-        <v>101</v>
-      </c>
-      <c r="H52" t="s">
-        <v>13</v>
-      </c>
-      <c r="K52" t="s">
-        <v>101</v>
-      </c>
-      <c r="L52" t="s">
-        <v>186</v>
-      </c>
-    </row>
-    <row r="53" spans="2:12" x14ac:dyDescent="0.45">
-      <c r="B53" t="s">
-        <v>8</v>
-      </c>
-      <c r="C53" t="s">
-        <v>8</v>
-      </c>
-      <c r="D53" t="s">
-        <v>9</v>
-      </c>
-      <c r="E53" t="s">
-        <v>102</v>
-      </c>
-      <c r="F53" t="s">
-        <v>18</v>
-      </c>
-      <c r="G53" t="s">
-        <v>103</v>
-      </c>
-      <c r="H53" t="s">
-        <v>13</v>
-      </c>
-      <c r="K53" t="s">
-        <v>103</v>
-      </c>
-      <c r="L53" t="s">
-        <v>187</v>
-      </c>
-    </row>
-    <row r="54" spans="2:12" x14ac:dyDescent="0.45">
-      <c r="B54" t="s">
-        <v>8</v>
-      </c>
-      <c r="C54" t="s">
-        <v>8</v>
-      </c>
-      <c r="D54" t="s">
-        <v>9</v>
-      </c>
-      <c r="E54" t="s">
-        <v>104</v>
-      </c>
-      <c r="F54" t="s">
-        <v>18</v>
-      </c>
-      <c r="G54" t="s">
-        <v>105</v>
-      </c>
-      <c r="H54" t="s">
-        <v>13</v>
-      </c>
-      <c r="K54" t="s">
-        <v>105</v>
-      </c>
-      <c r="L54" t="s">
-        <v>188</v>
-      </c>
-    </row>
-    <row r="55" spans="2:12" x14ac:dyDescent="0.45">
-      <c r="B55" t="s">
-        <v>8</v>
-      </c>
-      <c r="C55" t="s">
-        <v>8</v>
-      </c>
-      <c r="D55" t="s">
-        <v>9</v>
-      </c>
-      <c r="E55" t="s">
-        <v>106</v>
-      </c>
-      <c r="F55" t="s">
-        <v>18</v>
-      </c>
-      <c r="G55" t="s">
-        <v>107</v>
-      </c>
-      <c r="H55" t="s">
-        <v>13</v>
-      </c>
-      <c r="K55" t="s">
-        <v>107</v>
-      </c>
-      <c r="L55" t="s">
-        <v>189</v>
-      </c>
-    </row>
-    <row r="56" spans="2:12" x14ac:dyDescent="0.45">
-      <c r="B56" t="s">
-        <v>8</v>
-      </c>
-      <c r="C56" t="s">
-        <v>8</v>
-      </c>
-      <c r="D56" t="s">
-        <v>9</v>
-      </c>
-      <c r="E56" t="s">
-        <v>108</v>
-      </c>
-      <c r="F56" t="s">
-        <v>18</v>
-      </c>
-      <c r="G56" t="s">
-        <v>109</v>
-      </c>
-      <c r="H56" t="s">
-        <v>13</v>
-      </c>
-      <c r="K56" t="s">
-        <v>109</v>
-      </c>
-      <c r="L56" t="s">
-        <v>190</v>
-      </c>
-    </row>
-    <row r="57" spans="2:12" x14ac:dyDescent="0.45">
-      <c r="B57" t="s">
-        <v>8</v>
-      </c>
-      <c r="C57" t="s">
-        <v>8</v>
-      </c>
-      <c r="D57" t="s">
-        <v>9</v>
-      </c>
-      <c r="E57" t="s">
-        <v>110</v>
-      </c>
-      <c r="F57" t="s">
-        <v>10</v>
-      </c>
-      <c r="G57" t="s">
-        <v>111</v>
-      </c>
-      <c r="H57" t="s">
-        <v>13</v>
-      </c>
-      <c r="K57" t="s">
-        <v>111</v>
-      </c>
-      <c r="L57" t="s">
-        <v>191</v>
-      </c>
-    </row>
-    <row r="58" spans="2:12" x14ac:dyDescent="0.45">
-      <c r="B58" t="s">
-        <v>8</v>
-      </c>
-      <c r="C58" t="s">
-        <v>8</v>
-      </c>
-      <c r="D58" t="s">
-        <v>9</v>
-      </c>
-      <c r="E58" t="s">
-        <v>112</v>
-      </c>
-      <c r="F58" t="s">
-        <v>14</v>
-      </c>
-      <c r="G58" t="s">
-        <v>113</v>
-      </c>
-      <c r="H58" t="s">
-        <v>13</v>
-      </c>
-      <c r="K58" t="s">
-        <v>113</v>
-      </c>
-      <c r="L58" t="s">
-        <v>192</v>
-      </c>
-    </row>
-    <row r="59" spans="2:12" x14ac:dyDescent="0.45">
-      <c r="B59" t="s">
-        <v>8</v>
-      </c>
-      <c r="C59" t="s">
-        <v>8</v>
-      </c>
-      <c r="D59" t="s">
-        <v>9</v>
-      </c>
-      <c r="E59" t="s">
-        <v>114</v>
-      </c>
-      <c r="F59" t="s">
-        <v>14</v>
-      </c>
-      <c r="G59" t="s">
-        <v>115</v>
-      </c>
-      <c r="H59" t="s">
-        <v>13</v>
-      </c>
-      <c r="K59" t="s">
-        <v>115</v>
-      </c>
-      <c r="L59" t="s">
-        <v>193</v>
-      </c>
-    </row>
-    <row r="60" spans="2:12" x14ac:dyDescent="0.45">
-      <c r="B60" t="s">
-        <v>8</v>
-      </c>
-      <c r="C60" t="s">
-        <v>8</v>
-      </c>
-      <c r="D60" t="s">
-        <v>9</v>
-      </c>
-      <c r="E60" t="s">
-        <v>116</v>
-      </c>
-      <c r="F60" t="s">
-        <v>18</v>
-      </c>
-      <c r="G60" t="s">
-        <v>117</v>
-      </c>
-      <c r="H60" t="s">
-        <v>13</v>
-      </c>
-      <c r="K60" t="s">
-        <v>117</v>
-      </c>
-      <c r="L60" t="s">
-        <v>194</v>
-      </c>
-    </row>
-    <row r="61" spans="2:12" x14ac:dyDescent="0.45">
-      <c r="B61" t="s">
-        <v>8</v>
-      </c>
-      <c r="C61" t="s">
-        <v>8</v>
-      </c>
-      <c r="D61" t="s">
-        <v>9</v>
-      </c>
-      <c r="E61" t="s">
-        <v>118</v>
-      </c>
-      <c r="F61" t="s">
-        <v>10</v>
-      </c>
-      <c r="G61" t="s">
-        <v>119</v>
-      </c>
-      <c r="H61" t="s">
-        <v>13</v>
-      </c>
-      <c r="K61" t="s">
-        <v>119</v>
-      </c>
-      <c r="L61" t="s">
-        <v>195</v>
-      </c>
-    </row>
-    <row r="62" spans="2:12" x14ac:dyDescent="0.45">
-      <c r="B62" t="s">
-        <v>8</v>
-      </c>
-      <c r="C62" t="s">
-        <v>8</v>
-      </c>
-      <c r="D62" t="s">
-        <v>9</v>
-      </c>
-      <c r="E62" t="s">
-        <v>120</v>
-      </c>
-      <c r="F62" t="s">
-        <v>14</v>
-      </c>
-      <c r="G62" t="s">
-        <v>121</v>
-      </c>
-      <c r="H62" t="s">
-        <v>13</v>
-      </c>
-      <c r="K62" t="s">
-        <v>121</v>
-      </c>
-      <c r="L62" t="s">
-        <v>196</v>
-      </c>
-    </row>
-    <row r="63" spans="2:12" x14ac:dyDescent="0.45">
-      <c r="B63" t="s">
-        <v>8</v>
-      </c>
-      <c r="C63" t="s">
-        <v>8</v>
-      </c>
-      <c r="D63" t="s">
-        <v>9</v>
-      </c>
-      <c r="E63" t="s">
-        <v>122</v>
-      </c>
-      <c r="F63" t="s">
-        <v>16</v>
-      </c>
-      <c r="G63" t="s">
-        <v>123</v>
-      </c>
-      <c r="H63" t="s">
-        <v>13</v>
-      </c>
-      <c r="K63" t="s">
-        <v>123</v>
-      </c>
-      <c r="L63" t="s">
-        <v>197</v>
-      </c>
-    </row>
-    <row r="64" spans="2:12" x14ac:dyDescent="0.45">
-      <c r="B64" t="s">
-        <v>8</v>
-      </c>
-      <c r="C64" t="s">
-        <v>8</v>
-      </c>
-      <c r="D64" t="s">
-        <v>9</v>
-      </c>
-      <c r="E64" t="s">
-        <v>124</v>
-      </c>
-      <c r="F64" t="s">
-        <v>14</v>
-      </c>
-      <c r="G64" t="s">
         <v>125</v>
-      </c>
-      <c r="H64" t="s">
-        <v>13</v>
-      </c>
-      <c r="K64" t="s">
-        <v>125</v>
-      </c>
-      <c r="L64" t="s">
-        <v>198</v>
-      </c>
-    </row>
-    <row r="65" spans="2:12" x14ac:dyDescent="0.45">
-      <c r="B65" t="s">
-        <v>8</v>
-      </c>
-      <c r="C65" t="s">
-        <v>8</v>
-      </c>
-      <c r="D65" t="s">
-        <v>9</v>
-      </c>
-      <c r="E65" t="s">
-        <v>126</v>
-      </c>
-      <c r="F65" t="s">
-        <v>16</v>
-      </c>
-      <c r="G65" t="s">
-        <v>127</v>
-      </c>
-      <c r="H65" t="s">
-        <v>13</v>
-      </c>
-      <c r="K65" t="s">
-        <v>127</v>
-      </c>
-      <c r="L65" t="s">
-        <v>199</v>
-      </c>
-    </row>
-    <row r="66" spans="2:12" x14ac:dyDescent="0.45">
-      <c r="B66" t="s">
-        <v>8</v>
-      </c>
-      <c r="C66" t="s">
-        <v>8</v>
-      </c>
-      <c r="D66" t="s">
-        <v>9</v>
-      </c>
-      <c r="E66" t="s">
-        <v>128</v>
-      </c>
-      <c r="F66" t="s">
-        <v>31</v>
-      </c>
-      <c r="G66" t="s">
-        <v>129</v>
-      </c>
-      <c r="H66" t="s">
-        <v>13</v>
-      </c>
-      <c r="K66" t="s">
-        <v>129</v>
-      </c>
-      <c r="L66" t="s">
-        <v>200</v>
-      </c>
-    </row>
-    <row r="67" spans="2:12" x14ac:dyDescent="0.45">
-      <c r="B67" t="s">
-        <v>8</v>
-      </c>
-      <c r="C67" t="s">
-        <v>8</v>
-      </c>
-      <c r="D67" t="s">
-        <v>9</v>
-      </c>
-      <c r="E67" t="s">
-        <v>130</v>
-      </c>
-      <c r="F67" t="s">
-        <v>16</v>
-      </c>
-      <c r="G67" t="s">
-        <v>131</v>
-      </c>
-      <c r="H67" t="s">
-        <v>13</v>
-      </c>
-      <c r="K67" t="s">
-        <v>131</v>
-      </c>
-      <c r="L67" t="s">
-        <v>201</v>
-      </c>
-    </row>
-    <row r="68" spans="2:12" x14ac:dyDescent="0.45">
-      <c r="B68" t="s">
-        <v>8</v>
-      </c>
-      <c r="C68" t="s">
-        <v>8</v>
-      </c>
-      <c r="D68" t="s">
-        <v>9</v>
-      </c>
-      <c r="E68" t="s">
-        <v>132</v>
-      </c>
-      <c r="F68" t="s">
-        <v>11</v>
-      </c>
-      <c r="G68" t="s">
-        <v>133</v>
-      </c>
-      <c r="H68" t="s">
-        <v>13</v>
-      </c>
-      <c r="K68" t="s">
-        <v>133</v>
-      </c>
-      <c r="L68" t="s">
-        <v>202</v>
-      </c>
-    </row>
-    <row r="69" spans="2:12" x14ac:dyDescent="0.45">
-      <c r="B69" t="s">
-        <v>8</v>
-      </c>
-      <c r="C69" t="s">
-        <v>8</v>
-      </c>
-      <c r="D69" t="s">
-        <v>9</v>
-      </c>
-      <c r="E69" t="s">
-        <v>134</v>
-      </c>
-      <c r="F69" t="s">
-        <v>11</v>
-      </c>
-      <c r="G69" t="s">
-        <v>135</v>
-      </c>
-      <c r="H69" t="s">
-        <v>13</v>
-      </c>
-      <c r="K69" t="s">
-        <v>135</v>
-      </c>
-      <c r="L69" t="s">
-        <v>203</v>
       </c>
     </row>
   </sheetData>

--- a/VerveStacks_POL_grids_syn_5/SuppXLS/trades/scentrade__trade_links.xlsx
+++ b/VerveStacks_POL_grids_syn_5/SuppXLS/trades/scentrade__trade_links.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_POL_grids_syn_5\SuppXLS\trades\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{82FB81CC-E12A-4695-8381-533DE9A20F1D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{547283BF-26D8-44BB-99BD-A530D6E7D599}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{72EED2A6-0D28-44A6-A5EC-094DDCC1C001}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{848244A0-EDD6-49AA-B174-1E1371A86DD7}"/>
   </bookViews>
   <sheets>
     <sheet name="grid_links" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="362" uniqueCount="126">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="596" uniqueCount="204">
   <si>
     <t>~tradelinks_dins</t>
   </si>
@@ -260,12 +260,96 @@
     <t>g_sol9-dem4</t>
   </si>
   <si>
+    <t>e_wof0</t>
+  </si>
+  <si>
+    <t>g_wof0-gen2</t>
+  </si>
+  <si>
+    <t>e_wof1</t>
+  </si>
+  <si>
+    <t>g_wof1-dem0</t>
+  </si>
+  <si>
+    <t>e_wof10</t>
+  </si>
+  <si>
+    <t>g_wof10-gen4</t>
+  </si>
+  <si>
+    <t>e_wof2</t>
+  </si>
+  <si>
+    <t>g_wof2-gen4</t>
+  </si>
+  <si>
+    <t>e_wof3</t>
+  </si>
+  <si>
+    <t>g_wof3-dem0</t>
+  </si>
+  <si>
+    <t>e_wof4</t>
+  </si>
+  <si>
+    <t>g_wof4-gen4</t>
+  </si>
+  <si>
+    <t>e_wof5</t>
+  </si>
+  <si>
+    <t>g_wof5-gen4</t>
+  </si>
+  <si>
+    <t>e_wof6</t>
+  </si>
+  <si>
+    <t>g_wof6-gen4</t>
+  </si>
+  <si>
+    <t>e_wof7</t>
+  </si>
+  <si>
+    <t>g_wof7-gen3</t>
+  </si>
+  <si>
+    <t>e_wof8</t>
+  </si>
+  <si>
+    <t>g_wof8-gen4</t>
+  </si>
+  <si>
+    <t>e_wof9</t>
+  </si>
+  <si>
+    <t>g_wof9-gen4</t>
+  </si>
+  <si>
     <t>e_won0</t>
   </si>
   <si>
     <t>g_won0-gen0</t>
   </si>
   <si>
+    <t>e_won1</t>
+  </si>
+  <si>
+    <t>g_won1-gen0</t>
+  </si>
+  <si>
+    <t>e_won10</t>
+  </si>
+  <si>
+    <t>g_won10-gen4</t>
+  </si>
+  <si>
+    <t>e_won11</t>
+  </si>
+  <si>
+    <t>g_won11-dem2</t>
+  </si>
+  <si>
     <t>e_won12</t>
   </si>
   <si>
@@ -278,12 +362,84 @@
     <t>g_won13-dem2</t>
   </si>
   <si>
+    <t>e_won14</t>
+  </si>
+  <si>
+    <t>g_won14-dem2</t>
+  </si>
+  <si>
+    <t>e_won15</t>
+  </si>
+  <si>
+    <t>g_won15-dem1</t>
+  </si>
+  <si>
+    <t>e_won16</t>
+  </si>
+  <si>
+    <t>g_won16-dem3</t>
+  </si>
+  <si>
+    <t>e_won17</t>
+  </si>
+  <si>
+    <t>g_won17-dem3</t>
+  </si>
+  <si>
     <t>e_won18</t>
   </si>
   <si>
     <t>g_won18-dem2</t>
   </si>
   <si>
+    <t>e_won19</t>
+  </si>
+  <si>
+    <t>g_won19-dem1</t>
+  </si>
+  <si>
+    <t>e_won2</t>
+  </si>
+  <si>
+    <t>g_won2-dem3</t>
+  </si>
+  <si>
+    <t>e_won3</t>
+  </si>
+  <si>
+    <t>g_won3-dem4</t>
+  </si>
+  <si>
+    <t>e_won4</t>
+  </si>
+  <si>
+    <t>g_won4-dem3</t>
+  </si>
+  <si>
+    <t>e_won5</t>
+  </si>
+  <si>
+    <t>g_won5-dem4</t>
+  </si>
+  <si>
+    <t>e_won6</t>
+  </si>
+  <si>
+    <t>g_won6-gen1</t>
+  </si>
+  <si>
+    <t>e_won7</t>
+  </si>
+  <si>
+    <t>g_won7-dem4</t>
+  </si>
+  <si>
+    <t>e_won8</t>
+  </si>
+  <si>
+    <t>g_won8-dem0</t>
+  </si>
+  <si>
     <t>e_won9</t>
   </si>
   <si>
@@ -401,19 +557,97 @@
     <t>grid link -116.0 km- Potential connection: Renewable cluster 9 to Demand cluster 4</t>
   </si>
   <si>
+    <t>grid link -46.0 km- Potential connection: Renewable cluster 40 to Generation cluster 2</t>
+  </si>
+  <si>
+    <t>grid link -74.0 km- Potential connection: Renewable cluster 41 to Demand cluster 0</t>
+  </si>
+  <si>
+    <t>grid link -87.0 km- Potential connection: Renewable cluster 50 to Generation cluster 4</t>
+  </si>
+  <si>
+    <t>grid link -119.0 km- Potential connection: Renewable cluster 42 to Generation cluster 4</t>
+  </si>
+  <si>
+    <t>grid link -116.0 km- Potential connection: Renewable cluster 43 to Demand cluster 0</t>
+  </si>
+  <si>
+    <t>grid link -65.0 km- Potential connection: Renewable cluster 44 to Generation cluster 4</t>
+  </si>
+  <si>
+    <t>grid link -97.0 km- Potential connection: Renewable cluster 45 to Generation cluster 4</t>
+  </si>
+  <si>
+    <t>grid link -36.0 km- Potential connection: Renewable cluster 46 to Generation cluster 4</t>
+  </si>
+  <si>
+    <t>grid link -126.0 km- Potential connection: Renewable cluster 47 to Generation cluster 3</t>
+  </si>
+  <si>
+    <t>grid link -133.0 km- Potential connection: Renewable cluster 48 to Generation cluster 4</t>
+  </si>
+  <si>
+    <t>grid link -65.0 km- Potential connection: Renewable cluster 49 to Generation cluster 4</t>
+  </si>
+  <si>
     <t>grid link -43.0 km- Potential connection: Renewable cluster 20 to Generation cluster 0</t>
   </si>
   <si>
-    <t>grid link -0.0 km- Renewable cluster 32 to Demand cluster 2</t>
-  </si>
-  <si>
-    <t>grid link -0.0 km- Renewable cluster 33 to Demand cluster 2</t>
-  </si>
-  <si>
-    <t>grid link -0.0 km- Renewable cluster 38 to Demand cluster 2</t>
-  </si>
-  <si>
-    <t>grid link -0.0 km- Renewable cluster 29 to Demand cluster 0</t>
+    <t>grid link -94.0 km- Potential connection: Renewable cluster 21 to Generation cluster 0</t>
+  </si>
+  <si>
+    <t>grid link -118.0 km- Potential connection: Renewable cluster 30 to Generation cluster 4</t>
+  </si>
+  <si>
+    <t>grid link -113.0 km- Potential connection: Renewable cluster 31 to Demand cluster 2</t>
+  </si>
+  <si>
+    <t>grid link -94.0 km- Renewable cluster 32 to Demand cluster 2</t>
+  </si>
+  <si>
+    <t>grid link -71.0 km- Renewable cluster 33 to Demand cluster 2</t>
+  </si>
+  <si>
+    <t>grid link -99.0 km- Potential connection: Renewable cluster 34 to Demand cluster 2</t>
+  </si>
+  <si>
+    <t>grid link -131.0 km- Potential connection: Renewable cluster 35 to Demand cluster 1</t>
+  </si>
+  <si>
+    <t>grid link -145.0 km- Potential connection: Renewable cluster 36 to Demand cluster 3</t>
+  </si>
+  <si>
+    <t>grid link -123.0 km- Potential connection: Renewable cluster 37 to Demand cluster 3</t>
+  </si>
+  <si>
+    <t>grid link -199.0 km- Renewable cluster 38 to Demand cluster 2</t>
+  </si>
+  <si>
+    <t>grid link -48.0 km- Potential connection: Renewable cluster 39 to Demand cluster 1</t>
+  </si>
+  <si>
+    <t>grid link -52.0 km- Potential connection: Renewable cluster 22 to Demand cluster 3</t>
+  </si>
+  <si>
+    <t>grid link -68.0 km- Potential connection: Renewable cluster 23 to Demand cluster 4</t>
+  </si>
+  <si>
+    <t>grid link -121.0 km- Potential connection: Renewable cluster 24 to Demand cluster 3</t>
+  </si>
+  <si>
+    <t>grid link -159.0 km- Potential connection: Renewable cluster 25 to Demand cluster 4</t>
+  </si>
+  <si>
+    <t>grid link -30.0 km- Potential connection: Renewable cluster 26 to Generation cluster 1</t>
+  </si>
+  <si>
+    <t>grid link -77.0 km- Potential connection: Renewable cluster 27 to Demand cluster 4</t>
+  </si>
+  <si>
+    <t>grid link -176.0 km- Potential connection: Renewable cluster 28 to Demand cluster 0</t>
+  </si>
+  <si>
+    <t>grid link -38.0 km- Renewable cluster 29 to Demand cluster 0</t>
   </si>
 </sst>
 </file>
@@ -784,8 +1018,8 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E67131D7-2E3D-464C-9B01-C0892CEA7633}">
-  <dimension ref="B3:L43"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{803EF5A2-34A2-4BB9-A077-81EB35E837ED}">
+  <dimension ref="B3:L69"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
     <row r="3" spans="2:12" x14ac:dyDescent="0.45">
@@ -793,7 +1027,7 @@
         <v>0</v>
       </c>
       <c r="K3" t="s">
-        <v>84</v>
+        <v>136</v>
       </c>
     </row>
     <row r="4" spans="2:12" x14ac:dyDescent="0.45">
@@ -819,10 +1053,10 @@
         <v>7</v>
       </c>
       <c r="K4" t="s">
-        <v>85</v>
+        <v>137</v>
       </c>
       <c r="L4" t="s">
-        <v>86</v>
+        <v>138</v>
       </c>
     </row>
     <row r="5" spans="2:12" x14ac:dyDescent="0.45">
@@ -851,7 +1085,7 @@
         <v>12</v>
       </c>
       <c r="L5" t="s">
-        <v>87</v>
+        <v>139</v>
       </c>
     </row>
     <row r="6" spans="2:12" x14ac:dyDescent="0.45">
@@ -880,7 +1114,7 @@
         <v>15</v>
       </c>
       <c r="L6" t="s">
-        <v>88</v>
+        <v>140</v>
       </c>
     </row>
     <row r="7" spans="2:12" x14ac:dyDescent="0.45">
@@ -909,7 +1143,7 @@
         <v>17</v>
       </c>
       <c r="L7" t="s">
-        <v>89</v>
+        <v>141</v>
       </c>
     </row>
     <row r="8" spans="2:12" x14ac:dyDescent="0.45">
@@ -938,7 +1172,7 @@
         <v>19</v>
       </c>
       <c r="L8" t="s">
-        <v>90</v>
+        <v>142</v>
       </c>
     </row>
     <row r="9" spans="2:12" x14ac:dyDescent="0.45">
@@ -967,7 +1201,7 @@
         <v>21</v>
       </c>
       <c r="L9" t="s">
-        <v>91</v>
+        <v>143</v>
       </c>
     </row>
     <row r="10" spans="2:12" x14ac:dyDescent="0.45">
@@ -996,7 +1230,7 @@
         <v>22</v>
       </c>
       <c r="L10" t="s">
-        <v>92</v>
+        <v>144</v>
       </c>
     </row>
     <row r="11" spans="2:12" x14ac:dyDescent="0.45">
@@ -1025,7 +1259,7 @@
         <v>24</v>
       </c>
       <c r="L11" t="s">
-        <v>93</v>
+        <v>145</v>
       </c>
     </row>
     <row r="12" spans="2:12" x14ac:dyDescent="0.45">
@@ -1054,7 +1288,7 @@
         <v>25</v>
       </c>
       <c r="L12" t="s">
-        <v>94</v>
+        <v>146</v>
       </c>
     </row>
     <row r="13" spans="2:12" x14ac:dyDescent="0.45">
@@ -1083,7 +1317,7 @@
         <v>26</v>
       </c>
       <c r="L13" t="s">
-        <v>95</v>
+        <v>147</v>
       </c>
     </row>
     <row r="14" spans="2:12" x14ac:dyDescent="0.45">
@@ -1112,7 +1346,7 @@
         <v>27</v>
       </c>
       <c r="L14" t="s">
-        <v>96</v>
+        <v>148</v>
       </c>
     </row>
     <row r="15" spans="2:12" x14ac:dyDescent="0.45">
@@ -1141,7 +1375,7 @@
         <v>29</v>
       </c>
       <c r="L15" t="s">
-        <v>97</v>
+        <v>149</v>
       </c>
     </row>
     <row r="16" spans="2:12" x14ac:dyDescent="0.45">
@@ -1170,7 +1404,7 @@
         <v>30</v>
       </c>
       <c r="L16" t="s">
-        <v>98</v>
+        <v>150</v>
       </c>
     </row>
     <row r="17" spans="2:12" x14ac:dyDescent="0.45">
@@ -1199,7 +1433,7 @@
         <v>32</v>
       </c>
       <c r="L17" t="s">
-        <v>99</v>
+        <v>151</v>
       </c>
     </row>
     <row r="18" spans="2:12" x14ac:dyDescent="0.45">
@@ -1228,7 +1462,7 @@
         <v>33</v>
       </c>
       <c r="L18" t="s">
-        <v>100</v>
+        <v>152</v>
       </c>
     </row>
     <row r="19" spans="2:12" x14ac:dyDescent="0.45">
@@ -1257,7 +1491,7 @@
         <v>35</v>
       </c>
       <c r="L19" t="s">
-        <v>101</v>
+        <v>153</v>
       </c>
     </row>
     <row r="20" spans="2:12" x14ac:dyDescent="0.45">
@@ -1286,7 +1520,7 @@
         <v>37</v>
       </c>
       <c r="L20" t="s">
-        <v>102</v>
+        <v>154</v>
       </c>
     </row>
     <row r="21" spans="2:12" x14ac:dyDescent="0.45">
@@ -1315,7 +1549,7 @@
         <v>39</v>
       </c>
       <c r="L21" t="s">
-        <v>103</v>
+        <v>155</v>
       </c>
     </row>
     <row r="22" spans="2:12" x14ac:dyDescent="0.45">
@@ -1344,7 +1578,7 @@
         <v>41</v>
       </c>
       <c r="L22" t="s">
-        <v>104</v>
+        <v>156</v>
       </c>
     </row>
     <row r="23" spans="2:12" x14ac:dyDescent="0.45">
@@ -1373,7 +1607,7 @@
         <v>43</v>
       </c>
       <c r="L23" t="s">
-        <v>105</v>
+        <v>157</v>
       </c>
     </row>
     <row r="24" spans="2:12" x14ac:dyDescent="0.45">
@@ -1402,7 +1636,7 @@
         <v>45</v>
       </c>
       <c r="L24" t="s">
-        <v>106</v>
+        <v>158</v>
       </c>
     </row>
     <row r="25" spans="2:12" x14ac:dyDescent="0.45">
@@ -1431,7 +1665,7 @@
         <v>47</v>
       </c>
       <c r="L25" t="s">
-        <v>107</v>
+        <v>159</v>
       </c>
     </row>
     <row r="26" spans="2:12" x14ac:dyDescent="0.45">
@@ -1460,7 +1694,7 @@
         <v>49</v>
       </c>
       <c r="L26" t="s">
-        <v>108</v>
+        <v>160</v>
       </c>
     </row>
     <row r="27" spans="2:12" x14ac:dyDescent="0.45">
@@ -1489,7 +1723,7 @@
         <v>51</v>
       </c>
       <c r="L27" t="s">
-        <v>109</v>
+        <v>161</v>
       </c>
     </row>
     <row r="28" spans="2:12" x14ac:dyDescent="0.45">
@@ -1518,7 +1752,7 @@
         <v>53</v>
       </c>
       <c r="L28" t="s">
-        <v>110</v>
+        <v>162</v>
       </c>
     </row>
     <row r="29" spans="2:12" x14ac:dyDescent="0.45">
@@ -1547,7 +1781,7 @@
         <v>55</v>
       </c>
       <c r="L29" t="s">
-        <v>111</v>
+        <v>163</v>
       </c>
     </row>
     <row r="30" spans="2:12" x14ac:dyDescent="0.45">
@@ -1576,7 +1810,7 @@
         <v>57</v>
       </c>
       <c r="L30" t="s">
-        <v>112</v>
+        <v>164</v>
       </c>
     </row>
     <row r="31" spans="2:12" x14ac:dyDescent="0.45">
@@ -1605,7 +1839,7 @@
         <v>59</v>
       </c>
       <c r="L31" t="s">
-        <v>113</v>
+        <v>165</v>
       </c>
     </row>
     <row r="32" spans="2:12" x14ac:dyDescent="0.45">
@@ -1634,7 +1868,7 @@
         <v>61</v>
       </c>
       <c r="L32" t="s">
-        <v>114</v>
+        <v>166</v>
       </c>
     </row>
     <row r="33" spans="2:12" x14ac:dyDescent="0.45">
@@ -1663,7 +1897,7 @@
         <v>63</v>
       </c>
       <c r="L33" t="s">
-        <v>115</v>
+        <v>167</v>
       </c>
     </row>
     <row r="34" spans="2:12" x14ac:dyDescent="0.45">
@@ -1692,7 +1926,7 @@
         <v>65</v>
       </c>
       <c r="L34" t="s">
-        <v>116</v>
+        <v>168</v>
       </c>
     </row>
     <row r="35" spans="2:12" x14ac:dyDescent="0.45">
@@ -1721,7 +1955,7 @@
         <v>67</v>
       </c>
       <c r="L35" t="s">
-        <v>117</v>
+        <v>169</v>
       </c>
     </row>
     <row r="36" spans="2:12" x14ac:dyDescent="0.45">
@@ -1750,7 +1984,7 @@
         <v>69</v>
       </c>
       <c r="L36" t="s">
-        <v>118</v>
+        <v>170</v>
       </c>
     </row>
     <row r="37" spans="2:12" x14ac:dyDescent="0.45">
@@ -1779,7 +2013,7 @@
         <v>71</v>
       </c>
       <c r="L37" t="s">
-        <v>119</v>
+        <v>171</v>
       </c>
     </row>
     <row r="38" spans="2:12" x14ac:dyDescent="0.45">
@@ -1808,7 +2042,7 @@
         <v>73</v>
       </c>
       <c r="L38" t="s">
-        <v>120</v>
+        <v>172</v>
       </c>
     </row>
     <row r="39" spans="2:12" x14ac:dyDescent="0.45">
@@ -1825,7 +2059,7 @@
         <v>74</v>
       </c>
       <c r="F39" t="s">
-        <v>20</v>
+        <v>28</v>
       </c>
       <c r="G39" t="s">
         <v>75</v>
@@ -1837,7 +2071,7 @@
         <v>75</v>
       </c>
       <c r="L39" t="s">
-        <v>121</v>
+        <v>173</v>
       </c>
     </row>
     <row r="40" spans="2:12" x14ac:dyDescent="0.45">
@@ -1854,7 +2088,7 @@
         <v>76</v>
       </c>
       <c r="F40" t="s">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="G40" t="s">
         <v>77</v>
@@ -1866,7 +2100,7 @@
         <v>77</v>
       </c>
       <c r="L40" t="s">
-        <v>122</v>
+        <v>174</v>
       </c>
     </row>
     <row r="41" spans="2:12" x14ac:dyDescent="0.45">
@@ -1883,7 +2117,7 @@
         <v>78</v>
       </c>
       <c r="F41" t="s">
-        <v>18</v>
+        <v>34</v>
       </c>
       <c r="G41" t="s">
         <v>79</v>
@@ -1895,7 +2129,7 @@
         <v>79</v>
       </c>
       <c r="L41" t="s">
-        <v>123</v>
+        <v>175</v>
       </c>
     </row>
     <row r="42" spans="2:12" x14ac:dyDescent="0.45">
@@ -1912,7 +2146,7 @@
         <v>80</v>
       </c>
       <c r="F42" t="s">
-        <v>18</v>
+        <v>34</v>
       </c>
       <c r="G42" t="s">
         <v>81</v>
@@ -1924,7 +2158,7 @@
         <v>81</v>
       </c>
       <c r="L42" t="s">
-        <v>124</v>
+        <v>176</v>
       </c>
     </row>
     <row r="43" spans="2:12" x14ac:dyDescent="0.45">
@@ -1953,7 +2187,761 @@
         <v>83</v>
       </c>
       <c r="L43" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="44" spans="2:12" x14ac:dyDescent="0.45">
+      <c r="B44" t="s">
+        <v>8</v>
+      </c>
+      <c r="C44" t="s">
+        <v>8</v>
+      </c>
+      <c r="D44" t="s">
+        <v>9</v>
+      </c>
+      <c r="E44" t="s">
+        <v>84</v>
+      </c>
+      <c r="F44" t="s">
+        <v>34</v>
+      </c>
+      <c r="G44" t="s">
+        <v>85</v>
+      </c>
+      <c r="H44" t="s">
+        <v>13</v>
+      </c>
+      <c r="K44" t="s">
+        <v>85</v>
+      </c>
+      <c r="L44" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="45" spans="2:12" x14ac:dyDescent="0.45">
+      <c r="B45" t="s">
+        <v>8</v>
+      </c>
+      <c r="C45" t="s">
+        <v>8</v>
+      </c>
+      <c r="D45" t="s">
+        <v>9</v>
+      </c>
+      <c r="E45" t="s">
+        <v>86</v>
+      </c>
+      <c r="F45" t="s">
+        <v>34</v>
+      </c>
+      <c r="G45" t="s">
+        <v>87</v>
+      </c>
+      <c r="H45" t="s">
+        <v>13</v>
+      </c>
+      <c r="K45" t="s">
+        <v>87</v>
+      </c>
+      <c r="L45" t="s">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="46" spans="2:12" x14ac:dyDescent="0.45">
+      <c r="B46" t="s">
+        <v>8</v>
+      </c>
+      <c r="C46" t="s">
+        <v>8</v>
+      </c>
+      <c r="D46" t="s">
+        <v>9</v>
+      </c>
+      <c r="E46" t="s">
+        <v>88</v>
+      </c>
+      <c r="F46" t="s">
+        <v>34</v>
+      </c>
+      <c r="G46" t="s">
+        <v>89</v>
+      </c>
+      <c r="H46" t="s">
+        <v>13</v>
+      </c>
+      <c r="K46" t="s">
+        <v>89</v>
+      </c>
+      <c r="L46" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="47" spans="2:12" x14ac:dyDescent="0.45">
+      <c r="B47" t="s">
+        <v>8</v>
+      </c>
+      <c r="C47" t="s">
+        <v>8</v>
+      </c>
+      <c r="D47" t="s">
+        <v>9</v>
+      </c>
+      <c r="E47" t="s">
+        <v>90</v>
+      </c>
+      <c r="F47" t="s">
+        <v>31</v>
+      </c>
+      <c r="G47" t="s">
+        <v>91</v>
+      </c>
+      <c r="H47" t="s">
+        <v>13</v>
+      </c>
+      <c r="K47" t="s">
+        <v>91</v>
+      </c>
+      <c r="L47" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="48" spans="2:12" x14ac:dyDescent="0.45">
+      <c r="B48" t="s">
+        <v>8</v>
+      </c>
+      <c r="C48" t="s">
+        <v>8</v>
+      </c>
+      <c r="D48" t="s">
+        <v>9</v>
+      </c>
+      <c r="E48" t="s">
+        <v>92</v>
+      </c>
+      <c r="F48" t="s">
+        <v>34</v>
+      </c>
+      <c r="G48" t="s">
+        <v>93</v>
+      </c>
+      <c r="H48" t="s">
+        <v>13</v>
+      </c>
+      <c r="K48" t="s">
+        <v>93</v>
+      </c>
+      <c r="L48" t="s">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="49" spans="2:12" x14ac:dyDescent="0.45">
+      <c r="B49" t="s">
+        <v>8</v>
+      </c>
+      <c r="C49" t="s">
+        <v>8</v>
+      </c>
+      <c r="D49" t="s">
+        <v>9</v>
+      </c>
+      <c r="E49" t="s">
+        <v>94</v>
+      </c>
+      <c r="F49" t="s">
+        <v>34</v>
+      </c>
+      <c r="G49" t="s">
+        <v>95</v>
+      </c>
+      <c r="H49" t="s">
+        <v>13</v>
+      </c>
+      <c r="K49" t="s">
+        <v>95</v>
+      </c>
+      <c r="L49" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="50" spans="2:12" x14ac:dyDescent="0.45">
+      <c r="B50" t="s">
+        <v>8</v>
+      </c>
+      <c r="C50" t="s">
+        <v>8</v>
+      </c>
+      <c r="D50" t="s">
+        <v>9</v>
+      </c>
+      <c r="E50" t="s">
+        <v>96</v>
+      </c>
+      <c r="F50" t="s">
+        <v>20</v>
+      </c>
+      <c r="G50" t="s">
+        <v>97</v>
+      </c>
+      <c r="H50" t="s">
+        <v>13</v>
+      </c>
+      <c r="K50" t="s">
+        <v>97</v>
+      </c>
+      <c r="L50" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="51" spans="2:12" x14ac:dyDescent="0.45">
+      <c r="B51" t="s">
+        <v>8</v>
+      </c>
+      <c r="C51" t="s">
+        <v>8</v>
+      </c>
+      <c r="D51" t="s">
+        <v>9</v>
+      </c>
+      <c r="E51" t="s">
+        <v>98</v>
+      </c>
+      <c r="F51" t="s">
+        <v>20</v>
+      </c>
+      <c r="G51" t="s">
+        <v>99</v>
+      </c>
+      <c r="H51" t="s">
+        <v>13</v>
+      </c>
+      <c r="K51" t="s">
+        <v>99</v>
+      </c>
+      <c r="L51" t="s">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="52" spans="2:12" x14ac:dyDescent="0.45">
+      <c r="B52" t="s">
+        <v>8</v>
+      </c>
+      <c r="C52" t="s">
+        <v>8</v>
+      </c>
+      <c r="D52" t="s">
+        <v>9</v>
+      </c>
+      <c r="E52" t="s">
+        <v>100</v>
+      </c>
+      <c r="F52" t="s">
+        <v>34</v>
+      </c>
+      <c r="G52" t="s">
+        <v>101</v>
+      </c>
+      <c r="H52" t="s">
+        <v>13</v>
+      </c>
+      <c r="K52" t="s">
+        <v>101</v>
+      </c>
+      <c r="L52" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="53" spans="2:12" x14ac:dyDescent="0.45">
+      <c r="B53" t="s">
+        <v>8</v>
+      </c>
+      <c r="C53" t="s">
+        <v>8</v>
+      </c>
+      <c r="D53" t="s">
+        <v>9</v>
+      </c>
+      <c r="E53" t="s">
+        <v>102</v>
+      </c>
+      <c r="F53" t="s">
+        <v>18</v>
+      </c>
+      <c r="G53" t="s">
+        <v>103</v>
+      </c>
+      <c r="H53" t="s">
+        <v>13</v>
+      </c>
+      <c r="K53" t="s">
+        <v>103</v>
+      </c>
+      <c r="L53" t="s">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="54" spans="2:12" x14ac:dyDescent="0.45">
+      <c r="B54" t="s">
+        <v>8</v>
+      </c>
+      <c r="C54" t="s">
+        <v>8</v>
+      </c>
+      <c r="D54" t="s">
+        <v>9</v>
+      </c>
+      <c r="E54" t="s">
+        <v>104</v>
+      </c>
+      <c r="F54" t="s">
+        <v>18</v>
+      </c>
+      <c r="G54" t="s">
+        <v>105</v>
+      </c>
+      <c r="H54" t="s">
+        <v>13</v>
+      </c>
+      <c r="K54" t="s">
+        <v>105</v>
+      </c>
+      <c r="L54" t="s">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="55" spans="2:12" x14ac:dyDescent="0.45">
+      <c r="B55" t="s">
+        <v>8</v>
+      </c>
+      <c r="C55" t="s">
+        <v>8</v>
+      </c>
+      <c r="D55" t="s">
+        <v>9</v>
+      </c>
+      <c r="E55" t="s">
+        <v>106</v>
+      </c>
+      <c r="F55" t="s">
+        <v>18</v>
+      </c>
+      <c r="G55" t="s">
+        <v>107</v>
+      </c>
+      <c r="H55" t="s">
+        <v>13</v>
+      </c>
+      <c r="K55" t="s">
+        <v>107</v>
+      </c>
+      <c r="L55" t="s">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="56" spans="2:12" x14ac:dyDescent="0.45">
+      <c r="B56" t="s">
+        <v>8</v>
+      </c>
+      <c r="C56" t="s">
+        <v>8</v>
+      </c>
+      <c r="D56" t="s">
+        <v>9</v>
+      </c>
+      <c r="E56" t="s">
+        <v>108</v>
+      </c>
+      <c r="F56" t="s">
+        <v>18</v>
+      </c>
+      <c r="G56" t="s">
+        <v>109</v>
+      </c>
+      <c r="H56" t="s">
+        <v>13</v>
+      </c>
+      <c r="K56" t="s">
+        <v>109</v>
+      </c>
+      <c r="L56" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="57" spans="2:12" x14ac:dyDescent="0.45">
+      <c r="B57" t="s">
+        <v>8</v>
+      </c>
+      <c r="C57" t="s">
+        <v>8</v>
+      </c>
+      <c r="D57" t="s">
+        <v>9</v>
+      </c>
+      <c r="E57" t="s">
+        <v>110</v>
+      </c>
+      <c r="F57" t="s">
+        <v>10</v>
+      </c>
+      <c r="G57" t="s">
+        <v>111</v>
+      </c>
+      <c r="H57" t="s">
+        <v>13</v>
+      </c>
+      <c r="K57" t="s">
+        <v>111</v>
+      </c>
+      <c r="L57" t="s">
+        <v>191</v>
+      </c>
+    </row>
+    <row r="58" spans="2:12" x14ac:dyDescent="0.45">
+      <c r="B58" t="s">
+        <v>8</v>
+      </c>
+      <c r="C58" t="s">
+        <v>8</v>
+      </c>
+      <c r="D58" t="s">
+        <v>9</v>
+      </c>
+      <c r="E58" t="s">
+        <v>112</v>
+      </c>
+      <c r="F58" t="s">
+        <v>14</v>
+      </c>
+      <c r="G58" t="s">
+        <v>113</v>
+      </c>
+      <c r="H58" t="s">
+        <v>13</v>
+      </c>
+      <c r="K58" t="s">
+        <v>113</v>
+      </c>
+      <c r="L58" t="s">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="59" spans="2:12" x14ac:dyDescent="0.45">
+      <c r="B59" t="s">
+        <v>8</v>
+      </c>
+      <c r="C59" t="s">
+        <v>8</v>
+      </c>
+      <c r="D59" t="s">
+        <v>9</v>
+      </c>
+      <c r="E59" t="s">
+        <v>114</v>
+      </c>
+      <c r="F59" t="s">
+        <v>14</v>
+      </c>
+      <c r="G59" t="s">
+        <v>115</v>
+      </c>
+      <c r="H59" t="s">
+        <v>13</v>
+      </c>
+      <c r="K59" t="s">
+        <v>115</v>
+      </c>
+      <c r="L59" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="60" spans="2:12" x14ac:dyDescent="0.45">
+      <c r="B60" t="s">
+        <v>8</v>
+      </c>
+      <c r="C60" t="s">
+        <v>8</v>
+      </c>
+      <c r="D60" t="s">
+        <v>9</v>
+      </c>
+      <c r="E60" t="s">
+        <v>116</v>
+      </c>
+      <c r="F60" t="s">
+        <v>18</v>
+      </c>
+      <c r="G60" t="s">
+        <v>117</v>
+      </c>
+      <c r="H60" t="s">
+        <v>13</v>
+      </c>
+      <c r="K60" t="s">
+        <v>117</v>
+      </c>
+      <c r="L60" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="61" spans="2:12" x14ac:dyDescent="0.45">
+      <c r="B61" t="s">
+        <v>8</v>
+      </c>
+      <c r="C61" t="s">
+        <v>8</v>
+      </c>
+      <c r="D61" t="s">
+        <v>9</v>
+      </c>
+      <c r="E61" t="s">
+        <v>118</v>
+      </c>
+      <c r="F61" t="s">
+        <v>10</v>
+      </c>
+      <c r="G61" t="s">
+        <v>119</v>
+      </c>
+      <c r="H61" t="s">
+        <v>13</v>
+      </c>
+      <c r="K61" t="s">
+        <v>119</v>
+      </c>
+      <c r="L61" t="s">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="62" spans="2:12" x14ac:dyDescent="0.45">
+      <c r="B62" t="s">
+        <v>8</v>
+      </c>
+      <c r="C62" t="s">
+        <v>8</v>
+      </c>
+      <c r="D62" t="s">
+        <v>9</v>
+      </c>
+      <c r="E62" t="s">
+        <v>120</v>
+      </c>
+      <c r="F62" t="s">
+        <v>14</v>
+      </c>
+      <c r="G62" t="s">
+        <v>121</v>
+      </c>
+      <c r="H62" t="s">
+        <v>13</v>
+      </c>
+      <c r="K62" t="s">
+        <v>121</v>
+      </c>
+      <c r="L62" t="s">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="63" spans="2:12" x14ac:dyDescent="0.45">
+      <c r="B63" t="s">
+        <v>8</v>
+      </c>
+      <c r="C63" t="s">
+        <v>8</v>
+      </c>
+      <c r="D63" t="s">
+        <v>9</v>
+      </c>
+      <c r="E63" t="s">
+        <v>122</v>
+      </c>
+      <c r="F63" t="s">
+        <v>16</v>
+      </c>
+      <c r="G63" t="s">
+        <v>123</v>
+      </c>
+      <c r="H63" t="s">
+        <v>13</v>
+      </c>
+      <c r="K63" t="s">
+        <v>123</v>
+      </c>
+      <c r="L63" t="s">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="64" spans="2:12" x14ac:dyDescent="0.45">
+      <c r="B64" t="s">
+        <v>8</v>
+      </c>
+      <c r="C64" t="s">
+        <v>8</v>
+      </c>
+      <c r="D64" t="s">
+        <v>9</v>
+      </c>
+      <c r="E64" t="s">
+        <v>124</v>
+      </c>
+      <c r="F64" t="s">
+        <v>14</v>
+      </c>
+      <c r="G64" t="s">
         <v>125</v>
+      </c>
+      <c r="H64" t="s">
+        <v>13</v>
+      </c>
+      <c r="K64" t="s">
+        <v>125</v>
+      </c>
+      <c r="L64" t="s">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="65" spans="2:12" x14ac:dyDescent="0.45">
+      <c r="B65" t="s">
+        <v>8</v>
+      </c>
+      <c r="C65" t="s">
+        <v>8</v>
+      </c>
+      <c r="D65" t="s">
+        <v>9</v>
+      </c>
+      <c r="E65" t="s">
+        <v>126</v>
+      </c>
+      <c r="F65" t="s">
+        <v>16</v>
+      </c>
+      <c r="G65" t="s">
+        <v>127</v>
+      </c>
+      <c r="H65" t="s">
+        <v>13</v>
+      </c>
+      <c r="K65" t="s">
+        <v>127</v>
+      </c>
+      <c r="L65" t="s">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="66" spans="2:12" x14ac:dyDescent="0.45">
+      <c r="B66" t="s">
+        <v>8</v>
+      </c>
+      <c r="C66" t="s">
+        <v>8</v>
+      </c>
+      <c r="D66" t="s">
+        <v>9</v>
+      </c>
+      <c r="E66" t="s">
+        <v>128</v>
+      </c>
+      <c r="F66" t="s">
+        <v>23</v>
+      </c>
+      <c r="G66" t="s">
+        <v>129</v>
+      </c>
+      <c r="H66" t="s">
+        <v>13</v>
+      </c>
+      <c r="K66" t="s">
+        <v>129</v>
+      </c>
+      <c r="L66" t="s">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="67" spans="2:12" x14ac:dyDescent="0.45">
+      <c r="B67" t="s">
+        <v>8</v>
+      </c>
+      <c r="C67" t="s">
+        <v>8</v>
+      </c>
+      <c r="D67" t="s">
+        <v>9</v>
+      </c>
+      <c r="E67" t="s">
+        <v>130</v>
+      </c>
+      <c r="F67" t="s">
+        <v>16</v>
+      </c>
+      <c r="G67" t="s">
+        <v>131</v>
+      </c>
+      <c r="H67" t="s">
+        <v>13</v>
+      </c>
+      <c r="K67" t="s">
+        <v>131</v>
+      </c>
+      <c r="L67" t="s">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="68" spans="2:12" x14ac:dyDescent="0.45">
+      <c r="B68" t="s">
+        <v>8</v>
+      </c>
+      <c r="C68" t="s">
+        <v>8</v>
+      </c>
+      <c r="D68" t="s">
+        <v>9</v>
+      </c>
+      <c r="E68" t="s">
+        <v>132</v>
+      </c>
+      <c r="F68" t="s">
+        <v>11</v>
+      </c>
+      <c r="G68" t="s">
+        <v>133</v>
+      </c>
+      <c r="H68" t="s">
+        <v>13</v>
+      </c>
+      <c r="K68" t="s">
+        <v>133</v>
+      </c>
+      <c r="L68" t="s">
+        <v>202</v>
+      </c>
+    </row>
+    <row r="69" spans="2:12" x14ac:dyDescent="0.45">
+      <c r="B69" t="s">
+        <v>8</v>
+      </c>
+      <c r="C69" t="s">
+        <v>8</v>
+      </c>
+      <c r="D69" t="s">
+        <v>9</v>
+      </c>
+      <c r="E69" t="s">
+        <v>134</v>
+      </c>
+      <c r="F69" t="s">
+        <v>11</v>
+      </c>
+      <c r="G69" t="s">
+        <v>135</v>
+      </c>
+      <c r="H69" t="s">
+        <v>13</v>
+      </c>
+      <c r="K69" t="s">
+        <v>135</v>
+      </c>
+      <c r="L69" t="s">
+        <v>203</v>
       </c>
     </row>
   </sheetData>
